--- a/Data/EXCEL/Transfer/salemon/202208/8491-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/8491-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E80E1278-A99C-4C34-8A2B-8AD4F850DA9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44F3F157-922A-4634-A6FA-32AA106CDD85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="8491-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,16 +1227,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q85"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.625" customWidth="1"/>
-    <col min="2" max="6" width="4" customWidth="1"/>
-    <col min="7" max="7" width="8.375" customWidth="1"/>
-    <col min="8" max="16" width="12.5" customWidth="1"/>
-    <col min="17" max="17" width="13.125" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="7" width="13.5" customWidth="1"/>
+    <col min="8" max="16" width="14.25" customWidth="1"/>
+    <col min="17" max="17" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1255,7 +1262,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="33">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1294,7 +1301,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1337,7 +1344,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1376,7 +1383,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1429,7 +1436,7 @@
         <v>-60.9</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1482,7 +1489,7 @@
         <v>-62.2</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1535,7 +1542,7 @@
         <v>-61.6</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1588,7 +1595,7 @@
         <v>-60.8</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1641,7 +1648,7 @@
         <v>-62</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1694,7 +1701,7 @@
         <v>-65.8</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1747,7 +1754,7 @@
         <v>-59</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1800,7 +1807,7 @@
         <v>-36.299999999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1853,7 +1860,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1906,7 +1913,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1959,7 +1966,7 @@
         <v>64.099999999999994</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2012,7 +2019,7 @@
         <v>70.099999999999994</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2065,7 +2072,7 @@
         <v>86.2</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2118,7 +2125,7 @@
         <v>121.7</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2171,7 +2178,7 @@
         <v>138.80000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2224,7 +2231,7 @@
         <v>150.5</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2277,7 +2284,7 @@
         <v>148.69999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2330,7 +2337,7 @@
         <v>141.30000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2383,7 +2390,7 @@
         <v>118.6</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2436,7 +2443,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2489,7 +2496,7 @@
         <v>-48.4</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2542,7 +2549,7 @@
         <v>-51.4</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2595,7 +2602,7 @@
         <v>-53.3</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2648,7 +2655,7 @@
         <v>-55</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2701,7 +2708,7 @@
         <v>-57.8</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2754,7 +2761,7 @@
         <v>-63.8</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2807,7 +2814,7 @@
         <v>-66.099999999999994</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2860,7 +2867,7 @@
         <v>-67.3</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2913,7 +2920,7 @@
         <v>-66.2</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2966,7 +2973,7 @@
         <v>-64.3</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3019,7 +3026,7 @@
         <v>-64.900000000000006</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3072,7 +3079,7 @@
         <v>-62.6</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3125,7 +3132,7 @@
         <v>7.33</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3178,7 +3185,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3231,7 +3238,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3284,7 +3291,7 @@
         <v>30.7</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43678</v>
       </c>
@@ -3337,7 +3344,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43647</v>
       </c>
@@ -3390,7 +3397,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43617</v>
       </c>
@@ -3443,7 +3450,7 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43586</v>
       </c>
@@ -3496,7 +3503,7 @@
         <v>48.5</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43556</v>
       </c>
@@ -3549,7 +3556,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43525</v>
       </c>
@@ -3602,7 +3609,7 @@
         <v>41.7</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43497</v>
       </c>
@@ -3655,7 +3662,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43466</v>
       </c>
@@ -3708,7 +3715,7 @@
         <v>64.8</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43435</v>
       </c>
@@ -3761,7 +3768,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43405</v>
       </c>
@@ -3814,7 +3821,7 @@
         <v>8.59</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43374</v>
       </c>
@@ -3867,7 +3874,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43344</v>
       </c>
@@ -3920,7 +3927,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43313</v>
       </c>
@@ -3973,7 +3980,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1">
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>43282</v>
       </c>
@@ -4026,7 +4033,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>43252</v>
       </c>
@@ -4079,7 +4086,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>43221</v>
       </c>
@@ -4132,7 +4139,7 @@
         <v>63.6</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43191</v>
       </c>
@@ -4185,7 +4192,7 @@
         <v>90.4</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>43160</v>
       </c>
@@ -4238,7 +4245,7 @@
         <v>96.8</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="5" customFormat="1">
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>43132</v>
       </c>
@@ -4291,7 +4298,7 @@
         <v>104.4</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1">
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>43101</v>
       </c>
@@ -4344,7 +4351,7 @@
         <v>81.599999999999994</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1">
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>43070</v>
       </c>
@@ -4397,7 +4404,7 @@
         <v>76.3</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>43040</v>
       </c>
@@ -4450,7 +4457,7 @@
         <v>70.099999999999994</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="5" customFormat="1">
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>43009</v>
       </c>
@@ -4503,7 +4510,7 @@
         <v>62.9</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="5" customFormat="1">
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>42979</v>
       </c>
@@ -4556,7 +4563,7 @@
         <v>52.3</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="5" customFormat="1">
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>42948</v>
       </c>
@@ -4609,7 +4616,7 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="5" customFormat="1">
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>42917</v>
       </c>
@@ -4662,7 +4669,7 @@
         <v>38.6</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="5" customFormat="1">
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>42887</v>
       </c>
@@ -4715,7 +4722,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="5" customFormat="1">
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>42856</v>
       </c>
@@ -4768,7 +4775,7 @@
         <v>3.13</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="5" customFormat="1">
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>42826</v>
       </c>
@@ -4821,7 +4828,7 @@
         <v>-15</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="5" customFormat="1">
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>42795</v>
       </c>
@@ -4874,7 +4881,7 @@
         <v>-21.5</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="5" customFormat="1">
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>42767</v>
       </c>
@@ -4927,7 +4934,7 @@
         <v>-28.6</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="5" customFormat="1">
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>42736</v>
       </c>
@@ -4980,7 +4987,7 @@
         <v>-23.1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="5" customFormat="1">
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>42705</v>
       </c>
@@ -5033,7 +5040,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="74" spans="1:17" s="5" customFormat="1">
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>42675</v>
       </c>
@@ -5086,7 +5093,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="5" customFormat="1">
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>42644</v>
       </c>
@@ -5139,7 +5146,7 @@
         <v>7.95</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="5" customFormat="1">
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>42614</v>
       </c>
@@ -5192,7 +5199,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="5" customFormat="1">
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>42583</v>
       </c>
@@ -5245,7 +5252,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="5" customFormat="1">
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>42552</v>
       </c>
@@ -5298,7 +5305,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="79" spans="1:17" s="5" customFormat="1">
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>42522</v>
       </c>
@@ -5351,7 +5358,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="80" spans="1:17" s="5" customFormat="1">
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>42491</v>
       </c>
@@ -5404,7 +5411,7 @@
         <v>31.9</v>
       </c>
     </row>
-    <row r="81" spans="1:17" s="5" customFormat="1">
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>42461</v>
       </c>
@@ -5457,7 +5464,7 @@
         <v>47.3</v>
       </c>
     </row>
-    <row r="82" spans="1:17" s="5" customFormat="1">
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>42430</v>
       </c>
@@ -5510,7 +5517,7 @@
         <v>70.099999999999994</v>
       </c>
     </row>
-    <row r="83" spans="1:17" s="5" customFormat="1">
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>42401</v>
       </c>
@@ -5563,7 +5570,7 @@
         <v>90.6</v>
       </c>
     </row>
-    <row r="84" spans="1:17" s="5" customFormat="1">
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>42370</v>
       </c>
@@ -5616,7 +5623,7 @@
         <v>94.7</v>
       </c>
     </row>
-    <row r="85" spans="1:17" s="5" customFormat="1">
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>42339</v>
       </c>
@@ -5684,7 +5691,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>